--- a/hira_material_automation/output/master/hira_material_summary.xlsx
+++ b/hira_material_automation/output/master/hira_material_summary.xlsx
@@ -10,11 +10,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="040021_ALL SUTURE ANCHOR" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="040019_비금속성 ANCHOR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="041001_관절경 CANNULA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="040023_십자인대고정용 일차 고정재 - SCREW,B" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="040012_십자인대고정용-INTERFERENCE SCR" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="040028_1회용 관절 봉합용 NEEDLE(분리형)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'통합'!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'040021_ALL SUTURE ANCHOR'!$A$1:$J$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'040019_비금속성 ANCHOR'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'통합'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'040021_ALL SUTURE ANCHOR'!$A$1:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'040019_비금속성 ANCHOR'!$A$1:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'041001_관절경 CANNULA'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'040023_십자인대고정용 일차 고정재 - SCREW,B'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'040012_십자인대고정용-INTERFERENCE SCR'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'040028_1회용 관절 봉합용 NEEDLE(분리형)'!$A$1:$J$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,6 +438,389 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>연도</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>중분류코드</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>중분류명</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>건강보험 청구량</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>건강보험 청구금액</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>의료급여 청구량</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>의료급여 청구금액</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>청구량 합계</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>청구금액 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020년 01월</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>040012</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>십자인대고정용-INTERFERENCE SCREW(흡수성)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1557</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>219409741</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>6310870</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1602</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>225720611</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020년 01월</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>040019</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>20573</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>4285939178</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>695</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>142550377</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>21268</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>4428489555</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026년 01월</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>040019</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>25458</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>5640311240</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1021</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>224685140</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>26479</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>5864996380</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020년 01월</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>040021</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ALL SUTURE ANCHOR</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6593</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1238989831</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>31602059</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>6760</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>1270591890</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026년 01월</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>040021</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ALL SUTURE ANCHOR</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>8789</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1751250669</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>61530298</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>9102</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1812780967</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2020년 01월</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>040023</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>십자인대고정용 일차 고정재 - SCREW,BUTTON 등(금속류)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>964</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>171136102</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>5005736</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>176141838</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2020년 01월</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>040028</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1회용 관절 봉합용 NEEDLE(분리형)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>3659</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>292585626</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>8111454</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>3762</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>300697080</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2020년 01월</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>041001</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>관절경 CANNULA</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>20154</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>845399967</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>642</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>26888014</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>20796</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>872287981</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -500,39 +891,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026년 01월</t>
+          <t>2020년 01월</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>040019</t>
+          <t>040021</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비금속성 ANCHOR</t>
+          <t>ALL SUTURE ANCHOR</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>25458</v>
+        <v>6593</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5640311240</v>
+        <v>1238989831</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1021</v>
+        <v>167</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>224685140</v>
+        <v>31602059</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26479</v>
+        <v>6760</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>5864996380</v>
+        <v>1270591890</v>
       </c>
     </row>
     <row r="3">
@@ -575,123 +966,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J3"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>기간</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>연도</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>중분류코드</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>중분류명</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>건강보험 청구량</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>건강보험 청구금액</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>의료급여 청구량</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>의료급여 청구금액</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>청구량 합계</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>청구금액 합계</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026년 01월</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>040021</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ALL SUTURE ANCHOR</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>8789</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1751250669</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>313</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>61530298</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>9102</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>1812780967</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -702,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -772,39 +1046,194 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2020년 01월</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>040019</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>20573</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4285939178</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>695</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>142550377</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>21268</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>4428489555</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>2026년 01월</t>
         </is>
       </c>
+      <c r="B3" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>040019</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>25458</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>5640311240</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>1021</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>224685140</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>26479</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>5864996380</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>연도</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>중분류코드</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>중분류명</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>건강보험 청구량</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>건강보험 청구금액</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>의료급여 청구량</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>의료급여 청구금액</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>청구량 합계</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>청구금액 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020년 01월</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="n">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>040019</t>
+          <t>041001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비금속성 ANCHOR</t>
+          <t>관절경 CANNULA</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>25458</v>
+        <v>20154</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5640311240</v>
+        <v>845399967</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1021</v>
+        <v>642</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>224685140</v>
+        <v>26888014</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26479</v>
+        <v>20796</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>5864996380</v>
+        <v>872287981</v>
       </c>
     </row>
   </sheetData>
@@ -813,229 +1242,353 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x0101003A7F18B03E33BF4DA150962F23733248" ma:contentTypeVersion="13" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="00d5bc73201a7cf16b7b67444666f865">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9bf3fbf4-c6f4-4df2-8cf6-49e28bf51f66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aa075d809ae3b8704ec3701444232834" ns2:_="">
-    <xsd:import namespace="9bf3fbf4-c6f4-4df2-8cf6-49e28bf51f66"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9bf3fbf4-c6f4-4df2-8cf6-49e28bf51f66" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="이미지 태그" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="450bca00-d6b9-4d94-bef9-41f99f1b5cd1" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="20" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="콘텐츠 형식"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="제목"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>연도</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>중분류코드</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>중분류명</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>건강보험 청구량</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>건강보험 청구금액</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>의료급여 청구량</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>의료급여 청구금액</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>청구량 합계</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>청구금액 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020년 01월</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>040023</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>십자인대고정용 일차 고정재 - SCREW,BUTTON 등(금속류)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>964</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>171136102</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>5005736</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>176141838</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>연도</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>중분류코드</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>중분류명</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>건강보험 청구량</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>건강보험 청구금액</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>의료급여 청구량</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>의료급여 청구금액</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>청구량 합계</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>청구금액 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020년 01월</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>040012</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>십자인대고정용-INTERFERENCE SCREW(흡수성)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1557</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>219409741</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>6310870</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1602</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>225720611</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9bf3fbf4-c6f4-4df2-8cf6-49e28bf51f66">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40C5E1D9-644A-4A66-96A0-AF43E9001145}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8087E609-6535-415D-9728-DF1E50CB3AFA}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF07F697-99B7-4AA8-AF2C-1F676BBFEBBC}"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>연도</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>중분류코드</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>중분류명</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>건강보험 청구량</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>건강보험 청구금액</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>의료급여 청구량</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>의료급여 청구금액</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>청구량 합계</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>청구금액 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020년 01월</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>040028</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1회용 관절 봉합용 NEEDLE(분리형)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>3659</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>292585626</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>8111454</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>3762</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>300697080</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/hira_material_automation/output/master/hira_material_summary.xlsx
+++ b/hira_material_automation/output/master/hira_material_summary.xlsx
@@ -3259,7 +3259,11 @@
           <t>040012</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>십자인대고정용-INTERFERENCE SCREW(흡수성)</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="n">
         <v>1483</v>
       </c>
@@ -3293,7 +3297,11 @@
           <t>040012</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>십자인대고정용-INTERFERENCE SCREW(흡수성)</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="n">
         <v>1307</v>
       </c>
@@ -3327,7 +3335,11 @@
           <t>040012</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>십자인대고정용-INTERFERENCE SCREW(흡수성)</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="n">
         <v>1359</v>
       </c>
@@ -6097,7 +6109,11 @@
           <t>040019</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
       <c r="E149" s="2" t="n">
         <v>25458</v>
       </c>
@@ -6131,7 +6147,11 @@
           <t>040019</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
       <c r="E150" s="2" t="n">
         <v>25055</v>
       </c>
@@ -6165,7 +6185,11 @@
           <t>040019</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
       <c r="E151" s="2" t="n">
         <v>25898</v>
       </c>
@@ -8935,7 +8959,11 @@
           <t>040021</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ALL SUTURE ANCHOR</t>
+        </is>
+      </c>
       <c r="E224" s="2" t="n">
         <v>8789</v>
       </c>
@@ -8969,7 +8997,11 @@
           <t>040021</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ALL SUTURE ANCHOR</t>
+        </is>
+      </c>
       <c r="E225" s="2" t="n">
         <v>8336</v>
       </c>
@@ -9003,7 +9035,11 @@
           <t>040021</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ALL SUTURE ANCHOR</t>
+        </is>
+      </c>
       <c r="E226" s="2" t="n">
         <v>9265</v>
       </c>
@@ -11773,7 +11809,11 @@
           <t>040023</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>십자인대고정용 일차 고정재 - SCREW,BUTTON 등(금속류)</t>
+        </is>
+      </c>
       <c r="E299" s="2" t="n">
         <v>1155</v>
       </c>
@@ -11807,7 +11847,11 @@
           <t>040023</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>십자인대고정용 일차 고정재 - SCREW,BUTTON 등(금속류)</t>
+        </is>
+      </c>
       <c r="E300" s="2" t="n">
         <v>1081</v>
       </c>
@@ -11841,7 +11885,11 @@
           <t>040023</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>십자인대고정용 일차 고정재 - SCREW,BUTTON 등(금속류)</t>
+        </is>
+      </c>
       <c r="E301" s="2" t="n">
         <v>1249</v>
       </c>
@@ -14611,7 +14659,11 @@
           <t>040028</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>1회용 관절 봉합용 NEEDLE(분리형)</t>
+        </is>
+      </c>
       <c r="E374" s="2" t="n">
         <v>4556</v>
       </c>
@@ -14645,7 +14697,11 @@
           <t>040028</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>1회용 관절 봉합용 NEEDLE(분리형)</t>
+        </is>
+      </c>
       <c r="E375" s="2" t="n">
         <v>4479</v>
       </c>
@@ -14679,7 +14735,11 @@
           <t>040028</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>1회용 관절 봉합용 NEEDLE(분리형)</t>
+        </is>
+      </c>
       <c r="E376" s="2" t="n">
         <v>4836</v>
       </c>
@@ -17449,7 +17509,11 @@
           <t>041001</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>관절경 CANNULA</t>
+        </is>
+      </c>
       <c r="E449" s="2" t="n">
         <v>22435</v>
       </c>
@@ -17483,7 +17547,11 @@
           <t>041001</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>관절경 CANNULA</t>
+        </is>
+      </c>
       <c r="E450" s="2" t="n">
         <v>22600</v>
       </c>
@@ -17517,7 +17585,11 @@
           <t>041001</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>관절경 CANNULA</t>
+        </is>
+      </c>
       <c r="E451" s="2" t="n">
         <v>23752</v>
       </c>
@@ -19451,7 +19523,11 @@
           <t>250099</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>관절경 수술시 사용하는 활액 임시대체재</t>
+        </is>
+      </c>
       <c r="E502" s="2" t="n">
         <v>7662</v>
       </c>
@@ -19485,7 +19561,11 @@
           <t>250099</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>관절경 수술시 사용하는 활액 임시대체재</t>
+        </is>
+      </c>
       <c r="E503" s="2" t="n">
         <v>7784</v>
       </c>
@@ -19519,7 +19599,11 @@
           <t>250099</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>관절경 수술시 사용하는 활액 임시대체재</t>
+        </is>
+      </c>
       <c r="E504" s="2" t="n">
         <v>8415</v>
       </c>
@@ -22289,7 +22373,11 @@
           <t>900129</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>척추경막외 유착방지제</t>
+        </is>
+      </c>
       <c r="E577" s="2" t="n">
         <v>890</v>
       </c>
@@ -22323,7 +22411,11 @@
           <t>900129</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>척추경막외 유착방지제</t>
+        </is>
+      </c>
       <c r="E578" s="2" t="n">
         <v>992</v>
       </c>
@@ -22357,7 +22449,11 @@
           <t>900129</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>척추경막외 유착방지제</t>
+        </is>
+      </c>
       <c r="E579" s="2" t="n">
         <v>702</v>
       </c>
@@ -24370,7 +24466,11 @@
           <t>250099</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>관절경 수술시 사용하는 활액 임시대체재</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="n">
         <v>7662</v>
       </c>
@@ -24404,7 +24504,11 @@
           <t>250099</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>관절경 수술시 사용하는 활액 임시대체재</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="n">
         <v>7784</v>
       </c>
@@ -24438,7 +24542,11 @@
           <t>250099</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>관절경 수술시 사용하는 활액 임시대체재</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="n">
         <v>8415</v>
       </c>
@@ -27287,7 +27395,11 @@
           <t>040021</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ALL SUTURE ANCHOR</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="n">
         <v>8789</v>
       </c>
@@ -27321,7 +27433,11 @@
           <t>040021</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ALL SUTURE ANCHOR</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="n">
         <v>8336</v>
       </c>
@@ -27355,7 +27471,11 @@
           <t>040021</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ALL SUTURE ANCHOR</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="n">
         <v>9265</v>
       </c>
@@ -30204,7 +30324,11 @@
           <t>040019</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="n">
         <v>25458</v>
       </c>
@@ -30238,7 +30362,11 @@
           <t>040019</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="n">
         <v>25055</v>
       </c>
@@ -30272,7 +30400,11 @@
           <t>040019</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>비금속성 ANCHOR</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="n">
         <v>25898</v>
       </c>
@@ -33121,7 +33253,11 @@
           <t>041001</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>관절경 CANNULA</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="n">
         <v>22435</v>
       </c>
@@ -33155,7 +33291,11 @@
           <t>041001</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>관절경 CANNULA</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="n">
         <v>22600</v>
       </c>
@@ -33189,7 +33329,11 @@
           <t>041001</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>관절경 CANNULA</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="n">
         <v>23752</v>
       </c>
@@ -36038,7 +36182,11 @@
           <t>040023</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>십자인대고정용 일차 고정재 - SCREW,BUTTON 등(금속류)</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="n">
         <v>1155</v>
       </c>
@@ -36072,7 +36220,11 @@
           <t>040023</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>십자인대고정용 일차 고정재 - SCREW,BUTTON 등(금속류)</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="n">
         <v>1081</v>
       </c>
@@ -36106,7 +36258,11 @@
           <t>040023</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>십자인대고정용 일차 고정재 - SCREW,BUTTON 등(금속류)</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="n">
         <v>1249</v>
       </c>
@@ -38955,7 +39111,11 @@
           <t>040012</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>십자인대고정용-INTERFERENCE SCREW(흡수성)</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="n">
         <v>1483</v>
       </c>
@@ -38989,7 +39149,11 @@
           <t>040012</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>십자인대고정용-INTERFERENCE SCREW(흡수성)</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="n">
         <v>1307</v>
       </c>
@@ -39023,7 +39187,11 @@
           <t>040012</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>십자인대고정용-INTERFERENCE SCREW(흡수성)</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="n">
         <v>1359</v>
       </c>
@@ -41872,7 +42040,11 @@
           <t>040028</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1회용 관절 봉합용 NEEDLE(분리형)</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="n">
         <v>4556</v>
       </c>
@@ -41906,7 +42078,11 @@
           <t>040028</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1회용 관절 봉합용 NEEDLE(분리형)</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="n">
         <v>4479</v>
       </c>
@@ -41940,7 +42116,11 @@
           <t>040028</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1회용 관절 봉합용 NEEDLE(분리형)</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="n">
         <v>4836</v>
       </c>
@@ -44789,7 +44969,11 @@
           <t>900129</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>척추경막외 유착방지제</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="n">
         <v>890</v>
       </c>
@@ -44823,7 +45007,11 @@
           <t>900129</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>척추경막외 유착방지제</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="n">
         <v>992</v>
       </c>
@@ -44857,7 +45045,11 @@
           <t>900129</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>척추경막외 유착방지제</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="n">
         <v>702</v>
       </c>
